--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/export/TAB1.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/export/TAB1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satot\git\sqlapp\sqlapp-command\src\test\resources\com\sqlapp\data\db\command\export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29325061-CB78-4801-9690-C3415BF97F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D3E479-9B3D-4D2F-A06E-32B51785A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6108" yWindow="3876" windowWidth="20268" windowHeight="16188" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12876" yWindow="5100" windowWidth="19740" windowHeight="14928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,58 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{01669F00-8217-4661-B9FF-E628823E8126}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="游ゴシック"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>このSQLは1回だけ実行されます</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{5DE79060-264B-4455-9543-16F9FF023ED7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="游ゴシック"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>初期値取得用のSQLが返した行数を基準にデータの生成が実施されます</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{010421A5-0EDE-4280-BC96-A1C716B11BA7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="8"/>
+            <rFont val="游ゴシック"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>このSQLは1回だけ実行されます</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -66,7 +118,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -106,9 +158,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
-  <si>
-    <t>Table Name</t>
-  </si>
   <si>
     <t>TAB1</t>
   </si>
@@ -414,25 +463,6 @@
     <phoneticPr fontId="87"/>
   </si>
   <si>
-    <t>①Setup SQL
-[1 execution]</t>
-  </si>
-  <si>
-    <t>②Start Value
-[1 execution]</t>
-  </si>
-  <si>
-    <t>③Number of Rows</t>
-  </si>
-  <si>
-    <t>④Insert SQL
-[②×③ execution]</t>
-  </si>
-  <si>
-    <t>④Finalize SQL
-[1 execution]</t>
-  </si>
-  <si>
     <t>LocalDate.of(2025,4,1)</t>
   </si>
   <si>
@@ -458,6 +488,25 @@
     <t>TRUNCATE TABLE TAB1;
 SELECT COUNT(*) FROM TAB1</t>
     <phoneticPr fontId="87"/>
+  </si>
+  <si>
+    <t>テーブル名</t>
+  </si>
+  <si>
+    <t>[1] セットアップSQL</t>
+  </si>
+  <si>
+    <t>[2] 初期値取得用SQL</t>
+  </si>
+  <si>
+    <t>[3] 行数</t>
+  </si>
+  <si>
+    <t>[4] Insert SQL
+([2]×[3] 行 INSERT.)</t>
+  </si>
+  <si>
+    <t>[5] 終了処理用 SQL</t>
   </si>
 </sst>
 </file>
@@ -978,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1250,6 +1299,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1270,9 +1322,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1310,7 +1362,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1416,7 +1468,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1558,76 +1610,89 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.59765625" customWidth="1"/>
+    <col min="1" max="1" width="31.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="89" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="A4" s="89" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="129.6" x14ac:dyDescent="0.45">
+      <c r="A6" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="91"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A10" s="90" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="129.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="89" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="89">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="89" t="s">
-        <v>75</v>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="89" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1647,25 +1712,25 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1700,259 +1765,259 @@
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="89" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="89"/>
       <c r="F3" s="89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>15</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="89" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F4" s="89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>19</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="89" t="s">
+      <c r="F5" s="89" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="89" t="s">
-        <v>22</v>
       </c>
       <c r="G5" s="22"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>24</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="89" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="89" t="s">
-        <v>26</v>
       </c>
       <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>28</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="89" t="s">
         <v>29</v>
-      </c>
-      <c r="F7" s="89" t="s">
-        <v>30</v>
       </c>
       <c r="G7" s="30"/>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>31</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>32</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="89" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" s="89" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="34"/>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>35</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>36</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="89" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="89" t="s">
         <v>37</v>
-      </c>
-      <c r="F9" s="89" t="s">
-        <v>38</v>
       </c>
       <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>40</v>
       </c>
       <c r="C10" s="41"/>
       <c r="D10" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="F10" s="89" t="s">
         <v>42</v>
-      </c>
-      <c r="F10" s="89" t="s">
-        <v>43</v>
       </c>
       <c r="G10" s="42"/>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="F11" s="89" t="s">
         <v>42</v>
-      </c>
-      <c r="F11" s="89" t="s">
-        <v>43</v>
       </c>
       <c r="G11" s="46"/>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="48" t="s">
         <v>45</v>
-      </c>
-      <c r="B12" s="48" t="s">
-        <v>46</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G12" s="50"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="52" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>50</v>
       </c>
       <c r="C13" s="53"/>
       <c r="D13" s="89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="89"/>
       <c r="F13" s="89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="54"/>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="56" t="s">
         <v>52</v>
-      </c>
-      <c r="B14" s="56" t="s">
-        <v>53</v>
       </c>
       <c r="C14" s="57"/>
       <c r="D14" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="89"/>
       <c r="F14" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14" s="58"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" s="59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" s="89" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="62">
         <v>123</v>
@@ -1966,20 +2031,20 @@
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" s="63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="65"/>
       <c r="D16" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="89" t="s">
         <v>58</v>
-      </c>
-      <c r="F16" s="89" t="s">
-        <v>59</v>
       </c>
       <c r="G16" s="62">
         <v>123</v>
@@ -1993,20 +2058,20 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="68"/>
       <c r="D17" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="F17" s="89" t="s">
         <v>42</v>
-      </c>
-      <c r="F17" s="89" t="s">
-        <v>43</v>
       </c>
       <c r="G17" s="69">
         <v>1.2</v>
@@ -2020,83 +2085,83 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" s="89"/>
       <c r="F18" s="89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="87" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="88" t="s">
+      <c r="I18" s="88" t="s">
         <v>73</v>
-      </c>
-      <c r="I18" s="88" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="89" t="s">
         <v>63</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="75" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="89" t="s">
-        <v>64</v>
       </c>
       <c r="G19" s="76"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="89" t="s">
         <v>65</v>
-      </c>
-      <c r="B20" s="78" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="75" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="89" t="s">
-        <v>66</v>
       </c>
       <c r="E20" s="89"/>
       <c r="F20" s="89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" s="79"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="82"/>
       <c r="D21" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" s="89"/>
       <c r="F21" s="89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -2118,18 +2183,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="84" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="330" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
